--- a/docs/validacao-visual/2026-10-vendas-mapa/vendas-13-meses-selecionados.xlsx
+++ b/docs/validacao-visual/2026-10-vendas-mapa/vendas-13-meses-selecionados.xlsx
@@ -442,7 +442,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 16/10/2026, 10:47</v>
+        <v>Gerado em: 16/10/2026, 11:17</v>
       </c>
     </row>
     <row r="5">

--- a/docs/validacao-visual/2026-10-vendas-mapa/vendas-13-meses-selecionados.xlsx
+++ b/docs/validacao-visual/2026-10-vendas-mapa/vendas-13-meses-selecionados.xlsx
@@ -442,7 +442,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 16/10/2026, 11:17</v>
+        <v>Gerado em: 16/10/2026, 12:40</v>
       </c>
     </row>
     <row r="5">

--- a/docs/validacao-visual/2026-10-vendas-mapa/vendas-13-meses-selecionados.xlsx
+++ b/docs/validacao-visual/2026-10-vendas-mapa/vendas-13-meses-selecionados.xlsx
@@ -442,7 +442,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 26/10/2026, 11:15</v>
+        <v>Gerado em: 26/10/2026, 11:43</v>
       </c>
     </row>
     <row r="5">
